--- a/web/public/forms/orig/o-yejeong-gongjeongpyo.xlsx
+++ b/web/public/forms/orig/o-yejeong-gongjeongpyo.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\묘사소하천 정비공사(동산건설)\BGS\예정공정표\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13305" activeTab="1"/>

--- a/web/public/forms/orig/o-yejeong-gongjeongpyo.xlsx
+++ b/web/public/forms/orig/o-yejeong-gongjeongpyo.xlsx
@@ -1068,7 +1068,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="S1" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -10040,7 +10040,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="S1" s="46" t="inlineStr">
@@ -15627,7 +15627,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="R1" s="46" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="P1" s="46" t="inlineStr">

--- a/web/public/forms/orig/o-yejeong-gongjeongpyo.xlsx
+++ b/web/public/forms/orig/o-yejeong-gongjeongpyo.xlsx
@@ -908,7 +908,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="S1" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
